--- a/artfynd/Baksjökullen artfynd.xlsx
+++ b/artfynd/Baksjökullen artfynd.xlsx
@@ -31303,7 +31303,7 @@
         <v>132794181</v>
       </c>
       <c r="B295" t="n">
-        <v>91966</v>
+        <v>92027</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
